--- a/public/ProdukData/aksesoris.xlsx
+++ b/public/ProdukData/aksesoris.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="236">
   <si>
     <t>ID Sub Kategori</t>
   </si>
@@ -53,64 +53,676 @@
     <t>PPN 11%</t>
   </si>
   <si>
-    <t>ADAPTOR 20 WATT VANVO WHITE</t>
-  </si>
-  <si>
-    <t>ADAPTOR 20 WATT VANVO BLACK</t>
-  </si>
-  <si>
-    <t>KABEL CHARGER USB VANVO RED&amp;YELLOW</t>
-  </si>
-  <si>
-    <t>KABEL CHARGER USB VANVO WHITE&amp;YELLOW</t>
-  </si>
-  <si>
-    <t>KABEL CHARGER USB-C VANVO BLACK</t>
-  </si>
-  <si>
-    <t>KABEL CHARGER USB-C VANVO WHITE</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE X/XS/11PRO PANDA</t>
-  </si>
-  <si>
-    <t>TIDAK ADA GARANSI</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE XR/11 PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE XS MAX/11 PROMAX PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 12/12 PRO PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 12 PRO MAX PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 13/13PRO/14 PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 13 PRO MAX/14 PLUS PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 14PRO/15/16 PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGASS IPHONE 15 PRO PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 15 PROMAX PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE 15 PLUS/14 PRO MAX/16PLUS PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONE16 PRO/17/17PRO PANDA</t>
-  </si>
-  <si>
-    <t>TEMPERGLASS IPHONNE 16 PROMAX/17 PROMAX PANDA</t>
+    <t>KABEL LIGHTNING IPHONE TYPE B</t>
+  </si>
+  <si>
+    <t>KABEL LIGHTNING IPHONE TYPE C</t>
+  </si>
+  <si>
+    <t>KEPALA CASAN KAKI 3</t>
+  </si>
+  <si>
+    <t>KEPALA CASAN TYPE C</t>
+  </si>
+  <si>
+    <t>HEADSET IPHONE 7-14PM</t>
+  </si>
+  <si>
+    <t>HEADSET IPHONE 6-6SPLUS</t>
+  </si>
+  <si>
+    <t>GARSKIN REALME 10</t>
+  </si>
+  <si>
+    <t>KABEL DATA TYPE C FATA</t>
+  </si>
+  <si>
+    <t>TG ANTI SPY IPHONE 8</t>
+  </si>
+  <si>
+    <t>POWERBANK ROBOT 10000 mAh</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A17K</t>
+  </si>
+  <si>
+    <t>TG FULL XIOMI 10A</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE XR</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE X</t>
+  </si>
+  <si>
+    <t>TG FULL ANTI RADIASI SAM A20</t>
+  </si>
+  <si>
+    <t>TG FULL 11 PROMAX</t>
+  </si>
+  <si>
+    <t>HEADSET ORI COPOTAN IPHONE</t>
+  </si>
+  <si>
+    <t>KEPALA ORI TYPE C</t>
+  </si>
+  <si>
+    <t>case oppo a31</t>
+  </si>
+  <si>
+    <t>TG BIASA OPPO A31</t>
+  </si>
+  <si>
+    <t>TG FULL</t>
+  </si>
+  <si>
+    <t>TG ANTI SPY NOTE 9</t>
+  </si>
+  <si>
+    <t>ADAPTOR ANKER ORI</t>
+  </si>
+  <si>
+    <t>GLASS IPHONE XR WHITE</t>
+  </si>
+  <si>
+    <t>GLASS IPHONE XR YELLOW</t>
+  </si>
+  <si>
+    <t>GLASS IPHONE XR RED</t>
+  </si>
+  <si>
+    <t>GLASS IPHONE XR BLACK</t>
+  </si>
+  <si>
+    <t>GLASS + OCHA XR</t>
+  </si>
+  <si>
+    <t>GLASS + OCA IPHONE 11</t>
+  </si>
+  <si>
+    <t>GLASS + OCA 11 PRO</t>
+  </si>
+  <si>
+    <t>BACKGLASS IPHONE 11 PROMAX GRAY</t>
+  </si>
+  <si>
+    <t>KEPALA ADAPTOR IPHONE 20 WATT ORIGINAL</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO Y19</t>
+  </si>
+  <si>
+    <t>TG FULL ANDROID 1</t>
+  </si>
+  <si>
+    <t>CASE FUZE</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO FULL</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE 11 PRO</t>
+  </si>
+  <si>
+    <t>TG FULL 30</t>
+  </si>
+  <si>
+    <t>TG FULL ANDROID 2</t>
+  </si>
+  <si>
+    <t>TG FULL ANDROID 3</t>
+  </si>
+  <si>
+    <t>VIVO Y12S</t>
+  </si>
+  <si>
+    <t>OPPO F1 S</t>
+  </si>
+  <si>
+    <t>SAMSUNGA6</t>
+  </si>
+  <si>
+    <t>SAMSUNG A6</t>
+  </si>
+  <si>
+    <t>POCO X3</t>
+  </si>
+  <si>
+    <t>POCO  X3</t>
+  </si>
+  <si>
+    <t>SHARP AQUOS</t>
+  </si>
+  <si>
+    <t>SAMSUNG A04E</t>
+  </si>
+  <si>
+    <t>SAMSUNG A10S</t>
+  </si>
+  <si>
+    <t>KABEL LIGHTNING IPHONE TYPE C+Box</t>
+  </si>
+  <si>
+    <t>KEPALA CASAN TYPE C ori</t>
+  </si>
+  <si>
+    <t>HEADSET IPHONE 7-14PM+Box Ori</t>
+  </si>
+  <si>
+    <t>charging</t>
+  </si>
+  <si>
+    <t>TG FULL ANDROID</t>
+  </si>
+  <si>
+    <t>OPPO A3S</t>
+  </si>
+  <si>
+    <t>INFINIX 10 PLAY</t>
+  </si>
+  <si>
+    <t>INFINIX 10 PLAYY</t>
+  </si>
+  <si>
+    <t>REALME C15</t>
+  </si>
+  <si>
+    <t>XIAOMI</t>
+  </si>
+  <si>
+    <t>IPHONE XR</t>
+  </si>
+  <si>
+    <t>REDMI 9C</t>
+  </si>
+  <si>
+    <t>REDMI PRO 8A</t>
+  </si>
+  <si>
+    <t>IPHONE 11</t>
+  </si>
+  <si>
+    <t>CHARGER IPHONE</t>
+  </si>
+  <si>
+    <t>VIVO Z1 PRO</t>
+  </si>
+  <si>
+    <t>MEMORI 2GB</t>
+  </si>
+  <si>
+    <t>SAMSUNG A54</t>
+  </si>
+  <si>
+    <t>KABEL MIKRO VIVAN</t>
+  </si>
+  <si>
+    <t>TG FULL 12 PM</t>
+  </si>
+  <si>
+    <t>TG FULL IP 14 PRO</t>
+  </si>
+  <si>
+    <t>TG VIVO Y20</t>
+  </si>
+  <si>
+    <t>TG IPHONE XS</t>
+  </si>
+  <si>
+    <t>TG POCO F3</t>
+  </si>
+  <si>
+    <t>TG IPHONE 6</t>
+  </si>
+  <si>
+    <t>TG FULL IP XR</t>
+  </si>
+  <si>
+    <t>JELLY CASE IPHONE 14 PRO</t>
+  </si>
+  <si>
+    <t>OPPO RENO 5</t>
+  </si>
+  <si>
+    <t>TEMPERED GLASS OPPO RENO 5</t>
+  </si>
+  <si>
+    <t>TG REALME C11</t>
+  </si>
+  <si>
+    <t>JELLY CASE SAMSUNG A30</t>
+  </si>
+  <si>
+    <t>TG FULL IP 12</t>
+  </si>
+  <si>
+    <t>TG FULL RENO7 5G</t>
+  </si>
+  <si>
+    <t>CASE WARNA RENO7 5G</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A57</t>
+  </si>
+  <si>
+    <t>CASE OPPO A57</t>
+  </si>
+  <si>
+    <t>KABEL IPHONE USB</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG A6+</t>
+  </si>
+  <si>
+    <t>CASE OPPO A5S</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A5S</t>
+  </si>
+  <si>
+    <t>KABEL USB</t>
+  </si>
+  <si>
+    <t>KABEL BIASA</t>
+  </si>
+  <si>
+    <t>TG IPHONE XS MAX</t>
+  </si>
+  <si>
+    <t>CASE IPHONE XS MAX</t>
+  </si>
+  <si>
+    <t>TG FUL IP 15 PM</t>
+  </si>
+  <si>
+    <t>CASE MASES IP 12</t>
+  </si>
+  <si>
+    <t>GARSKIN</t>
+  </si>
+  <si>
+    <t>CASE MASES IP 15 PM</t>
+  </si>
+  <si>
+    <t>TG FULL IP 7 PLUS</t>
+  </si>
+  <si>
+    <t>GLASS IP XS MAX</t>
+  </si>
+  <si>
+    <t>TG FULL IP 11</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 15 PRO</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 12 PRO MAX</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 14 PRO MAX</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 15 PRO MAX</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 14 PRO</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE XR</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 11</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 11 PRO</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 11 PRO MAX</t>
+  </si>
+  <si>
+    <t>CLEAR CASE MAGNETIC IPHONE 13 PRO MAX</t>
+  </si>
+  <si>
+    <t>HEADSET IP ORI</t>
+  </si>
+  <si>
+    <t>TG FULL IP 8</t>
+  </si>
+  <si>
+    <t>TG OPPO A1K</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A77S</t>
+  </si>
+  <si>
+    <t>KABEL VIVAN TYPE C</t>
+  </si>
+  <si>
+    <t>KABEL DATA VIVAN TIPE C</t>
+  </si>
+  <si>
+    <t>HEADSET ANDROID BIASA</t>
+  </si>
+  <si>
+    <t>YG FULL VIVO S1 PRO</t>
+  </si>
+  <si>
+    <t>TG GULL IP 11</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE 11</t>
+  </si>
+  <si>
+    <t>TG FULL V5S</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO V25E</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO</t>
+  </si>
+  <si>
+    <t>FLASHDISK</t>
+  </si>
+  <si>
+    <t>OTG USB</t>
+  </si>
+  <si>
+    <t>CASE VIVO V29E</t>
+  </si>
+  <si>
+    <t>TG FULL IP 11 PRO</t>
+  </si>
+  <si>
+    <t>CHARGER VIVO S1</t>
+  </si>
+  <si>
+    <t>KABEL VIVAN TYPE B</t>
+  </si>
+  <si>
+    <t>TG BIASA VIVO V5S</t>
+  </si>
+  <si>
+    <t>KABEL CHARGER TYPE B</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG</t>
+  </si>
+  <si>
+    <t>KABEL IPHONE ORI</t>
+  </si>
+  <si>
+    <t>TG FULL IP 13</t>
+  </si>
+  <si>
+    <t>KABEL CHARGER IPHONE</t>
+  </si>
+  <si>
+    <t>TG FULL REALME C15</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A16</t>
+  </si>
+  <si>
+    <t>CASE OPPO F9</t>
+  </si>
+  <si>
+    <t>TG SAMSUNG A02S</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG A71</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO Y17S</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE 7 PLUS</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO Y02</t>
+  </si>
+  <si>
+    <t>TG FULL INFINIX SMART 5</t>
+  </si>
+  <si>
+    <t>CASE VIVO Y02</t>
+  </si>
+  <si>
+    <t>TG BIASA IP 11</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG A05</t>
+  </si>
+  <si>
+    <t>TG FULL IP11</t>
+  </si>
+  <si>
+    <t>CASE IP 11</t>
+  </si>
+  <si>
+    <t>TG FULL INFINIX SMART 8</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG A12</t>
+  </si>
+  <si>
+    <t>ADAPTOR IPHONE ORI 20 WATT</t>
+  </si>
+  <si>
+    <t>TG FULL 11</t>
+  </si>
+  <si>
+    <t>TG FULL XR</t>
+  </si>
+  <si>
+    <t>KABEL DATA T-C</t>
+  </si>
+  <si>
+    <t>TG ANTI SPAY</t>
+  </si>
+  <si>
+    <t>TG VIVO Y 17S</t>
+  </si>
+  <si>
+    <t>TG FULL REDMI 13C</t>
+  </si>
+  <si>
+    <t>TG OPPO A70</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO RENO  7</t>
+  </si>
+  <si>
+    <t>KABEL VIVAN</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG A30</t>
+  </si>
+  <si>
+    <t>CASE SAMSUNG A30</t>
+  </si>
+  <si>
+    <t>TG FULL SAMS A23 4G</t>
+  </si>
+  <si>
+    <t>PALA CHARGING ANDROID</t>
+  </si>
+  <si>
+    <t>TG FULL REDMI NOTE 7</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO A54</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO V11</t>
+  </si>
+  <si>
+    <t>TG FULL SAMSUNG M26</t>
+  </si>
+  <si>
+    <t>TG FULL POCO F3</t>
+  </si>
+  <si>
+    <t>TEMPERED GLASS FULL IP 11</t>
+  </si>
+  <si>
+    <t>ANTI GORES IPHONE XR</t>
+  </si>
+  <si>
+    <t>TEMPERED GLASS FULL IP 13</t>
+  </si>
+  <si>
+    <t>CLEAR CASE IP 13</t>
+  </si>
+  <si>
+    <t>KABEL CAS IPHONE</t>
+  </si>
+  <si>
+    <t>TG FULL REALME C12</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO Y91C</t>
+  </si>
+  <si>
+    <t>TG FULL REDMI NOTE 12</t>
+  </si>
+  <si>
+    <t>CLEAR CASE IPHONE 15</t>
+  </si>
+  <si>
+    <t>JELLY CASE 8+</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO V9</t>
+  </si>
+  <si>
+    <t>KEPALA CHARGER ROBOT</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE 12 MINI</t>
+  </si>
+  <si>
+    <t>TG FULL REDMI NOTE 9 PRO</t>
+  </si>
+  <si>
+    <t>TG BIASA SAMSUNG A05</t>
+  </si>
+  <si>
+    <t>TG FULL IPHONE 7+</t>
+  </si>
+  <si>
+    <t>TEMPERED FULL IPHONE 11</t>
+  </si>
+  <si>
+    <t>TEMPERED FULL IPHONE 11 PM</t>
+  </si>
+  <si>
+    <t>TEMPERED FULL IP XR</t>
+  </si>
+  <si>
+    <t>CASE IPHONE XR ANTI JAMUR</t>
+  </si>
+  <si>
+    <t>TG BIASA OPPO A5S</t>
+  </si>
+  <si>
+    <t>TEMPERED GLASS FULL IPHONE 11</t>
+  </si>
+  <si>
+    <t>TEMPERED FULL IPHONE XR</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO RENO 5F</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO F1S</t>
+  </si>
+  <si>
+    <t>CASE ANTI JAMUR OPPO A95</t>
+  </si>
+  <si>
+    <t>CASE OPPO RENO 7 5G</t>
+  </si>
+  <si>
+    <t>TG VIVO</t>
+  </si>
+  <si>
+    <t>TG BIASA REDMI 9</t>
+  </si>
+  <si>
+    <t>KEPALA CAS ROBOT</t>
+  </si>
+  <si>
+    <t>TG FULL VIVO Y21</t>
+  </si>
+  <si>
+    <t>KABEL CAS TYPE C</t>
+  </si>
+  <si>
+    <t>CASE VIVO Y21</t>
+  </si>
+  <si>
+    <t>TG ANTI SPAY REDMI 9A</t>
+  </si>
+  <si>
+    <t>KABEL DATA ANDROID</t>
+  </si>
+  <si>
+    <t>TG ANTI SPAY 15 PM</t>
+  </si>
+  <si>
+    <t>TG FULL POCO</t>
+  </si>
+  <si>
+    <t>TG FULL OPPO F9</t>
+  </si>
+  <si>
+    <t>TG  IASA OPPO F5</t>
+  </si>
+  <si>
+    <t>CASE SAMSUNG A12</t>
+  </si>
+  <si>
+    <t>KEPALA CASSAN  ROBOT</t>
+  </si>
+  <si>
+    <t>CASE OPPO A54</t>
+  </si>
+  <si>
+    <t>TG IP XR</t>
+  </si>
+  <si>
+    <t>TG FULL BIASA VIVO Y51</t>
+  </si>
+  <si>
+    <t>TG XR</t>
+  </si>
+  <si>
+    <t>KABEL DATA VIVAN</t>
+  </si>
+  <si>
+    <t>KEPALA ROBOT</t>
+  </si>
+  <si>
+    <t>CASE OPPO 92</t>
+  </si>
+  <si>
+    <t>POWER ADAPTER USB-C</t>
+  </si>
+  <si>
+    <t>APPLE USB-C 20WATT ORI TAM</t>
+  </si>
+  <si>
+    <t>TEMPERGLASS PANDA CLEAR IPHONE XR/11</t>
+  </si>
+  <si>
+    <t>ADAPTOR VANVO 20 WATT ORIGINAL WHITE</t>
+  </si>
+  <si>
+    <t>CV-01</t>
   </si>
 </sst>
 </file>
@@ -460,11 +1072,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L223"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="60.128" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="45.846" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="5.856" bestFit="true" customWidth="true" style="0"/>
@@ -472,7 +1084,7 @@
     <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="31.707" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="25.851" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="9.283" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -517,466 +1129,322 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
       <c r="I2">
-        <v>95000</v>
-      </c>
-      <c r="K2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
-        <v>95000</v>
-      </c>
-      <c r="K3">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
-        <v>65000</v>
-      </c>
-      <c r="K4">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I5">
-        <v>65000</v>
-      </c>
-      <c r="K5">
-        <v>180</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
-        <v>65000</v>
-      </c>
-      <c r="K6">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
-        <v>65000</v>
-      </c>
-      <c r="K7">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>263</v>
       </c>
       <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I8">
-        <v>50000</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>263</v>
       </c>
       <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I9">
         <v>50000</v>
       </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I10">
-        <v>50000</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>16</v>
+        <v>263</v>
       </c>
       <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="I11">
-        <v>50000</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E12">
-        <v>4</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I12">
-        <v>50000</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="E13">
-        <v>51</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I13">
         <v>50000</v>
       </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>5</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I14">
-        <v>50000</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>5</v>
-      </c>
-      <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I15">
-        <v>50000</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I16">
         <v>50000</v>
       </c>
-      <c r="K16" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17">
-        <v>462</v>
+        <v>263</v>
       </c>
       <c r="E17">
-        <v>5</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I17">
         <v>50000</v>
-      </c>
-      <c r="K17" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -984,86 +1452,4146 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>499</v>
+        <v>263</v>
       </c>
       <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I18">
-        <v>50000</v>
-      </c>
-      <c r="K18" t="s">
-        <v>19</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19">
-        <v>478</v>
+        <v>263</v>
       </c>
       <c r="E19">
-        <v>5</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="I19">
-        <v>50000</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>42</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>25000</v>
+      </c>
+      <c r="I20">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>5000</v>
+      </c>
+      <c r="I21">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>263</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>50000</v>
+      </c>
+      <c r="I22">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>263</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>40000</v>
+      </c>
+      <c r="I23">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24">
+        <v>263</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>150000</v>
+      </c>
+      <c r="I24">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>50000</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>50000</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>50000</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>50000</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>263</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>60000</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>60000</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31">
+        <v>263</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>80000</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>120000</v>
+      </c>
+      <c r="I32">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33">
+        <v>263</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>340000</v>
+      </c>
+      <c r="I33">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34">
+        <v>145</v>
+      </c>
+      <c r="E34">
         <v>9</v>
       </c>
-      <c r="B20" t="s">
+      <c r="G34">
+        <v>10000</v>
+      </c>
+      <c r="I34">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35">
+        <v>263</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>5000</v>
+      </c>
+      <c r="I35">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36">
+        <v>263</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="G36">
+        <v>25000</v>
+      </c>
+      <c r="I36">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37">
+        <v>264</v>
+      </c>
+      <c r="E37">
+        <v>9</v>
+      </c>
+      <c r="G37">
+        <v>5000</v>
+      </c>
+      <c r="I37">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38">
+        <v>216</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <v>5000</v>
+      </c>
+      <c r="I38">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>5000</v>
+      </c>
+      <c r="I39">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <v>263</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>5000</v>
+      </c>
+      <c r="I40">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41">
+        <v>263</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>10000</v>
+      </c>
+      <c r="I41">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42">
+        <v>263</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>5500</v>
+      </c>
+      <c r="I42">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43">
+        <v>139</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>5000</v>
+      </c>
+      <c r="I43">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44">
+        <v>53</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>25000</v>
+      </c>
+      <c r="I44">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45">
+        <v>127</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>75000</v>
+      </c>
+      <c r="I45">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46">
+        <v>127</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>5000</v>
+      </c>
+      <c r="I46">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47">
+        <v>263</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>5000</v>
+      </c>
+      <c r="I47">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48">
+        <v>263</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>25000</v>
+      </c>
+      <c r="I48">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49">
+        <v>263</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>5000</v>
+      </c>
+      <c r="I49">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50">
+        <v>210</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>5000</v>
+      </c>
+      <c r="I50">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51">
+        <v>124</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>5000</v>
+      </c>
+      <c r="I51">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52">
+        <v>263</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53">
+        <v>263</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54">
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54">
+        <v>26</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55">
+        <v>263</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>20000</v>
+      </c>
+      <c r="I55">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56">
+        <v>263</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>5000</v>
+      </c>
+      <c r="I56">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57">
+        <v>30</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>20000</v>
+      </c>
+      <c r="I57">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58">
+        <v>263</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>25000</v>
+      </c>
+      <c r="I58">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59">
+        <v>263</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>10000</v>
+      </c>
+      <c r="I59">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60">
+        <v>263</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>5000</v>
+      </c>
+      <c r="I60">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61">
+        <v>258</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>65000</v>
+      </c>
+      <c r="I61">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62">
+        <v>12</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>5000</v>
+      </c>
+      <c r="I62">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63">
+        <v>144</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>5000</v>
+      </c>
+      <c r="I63">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64">
+        <v>144</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>5000</v>
+      </c>
+      <c r="I64">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>5000</v>
+      </c>
+      <c r="I65">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66">
+        <v>263</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>50000</v>
+      </c>
+      <c r="I66">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67">
+        <v>118</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>5000</v>
+      </c>
+      <c r="I67">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68">
+        <v>18</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68">
+        <v>263</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>35000</v>
+      </c>
+      <c r="I68">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69">
+        <v>263</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>10000</v>
+      </c>
+      <c r="I69">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70">
+        <v>263</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>15000</v>
+      </c>
+      <c r="I70">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71">
+        <v>263</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>10000</v>
+      </c>
+      <c r="I71">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72">
+        <v>25</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>20000</v>
+      </c>
+      <c r="I72">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73">
+        <v>237</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>5000</v>
+      </c>
+      <c r="I73">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74">
+        <v>11</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>5000</v>
+      </c>
+      <c r="I74">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75">
+        <v>263</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>5000</v>
+      </c>
+      <c r="I75">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>10000</v>
+      </c>
+      <c r="I76">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77">
+        <v>12</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>5000</v>
+      </c>
+      <c r="I77">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78">
+        <v>25</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>20000</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79">
+        <v>260</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>10000</v>
+      </c>
+      <c r="I79">
+        <v>35000</v>
+      </c>
+      <c r="J79" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80">
+        <v>263</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>10000</v>
+      </c>
+      <c r="I80">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81">
+        <v>238</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>10000</v>
+      </c>
+      <c r="I81">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82">
+        <v>16</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>10000</v>
+      </c>
+      <c r="I82">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>94</v>
+      </c>
+      <c r="C83">
+        <v>263</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>10000</v>
+      </c>
+      <c r="I83">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84">
+        <v>263</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>25000</v>
+      </c>
+      <c r="I84">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85">
+        <v>231</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>5000</v>
+      </c>
+      <c r="I85">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86">
+        <v>231</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>25000</v>
+      </c>
+      <c r="I86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>98</v>
+      </c>
+      <c r="C87">
+        <v>263</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>5000</v>
+      </c>
+      <c r="I87">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>99</v>
+      </c>
+      <c r="C88">
         <v>31</v>
       </c>
-      <c r="C20">
-        <v>500</v>
-      </c>
-      <c r="E20">
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>10000</v>
+      </c>
+      <c r="I88">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89">
         <v>5</v>
       </c>
-      <c r="F20">
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89">
+        <v>81</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>25000</v>
+      </c>
+      <c r="I89">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90">
+        <v>81</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>10000</v>
+      </c>
+      <c r="I90">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91">
+        <v>263</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>5000</v>
+      </c>
+      <c r="I91">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92">
+        <v>4</v>
+      </c>
+      <c r="B92" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92">
+        <v>263</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>15000</v>
+      </c>
+      <c r="I92">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>104</v>
+      </c>
+      <c r="C93">
+        <v>52</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>5000</v>
+      </c>
+      <c r="I93">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94">
+        <v>52</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>65000</v>
+      </c>
+      <c r="I94">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95">
+        <v>7</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95">
+        <v>148</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>25000</v>
+      </c>
+      <c r="I95">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96">
+        <v>16</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>150000</v>
+      </c>
+      <c r="I96">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97">
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97">
+        <v>263</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>15000</v>
+      </c>
+      <c r="I97">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>109</v>
+      </c>
+      <c r="C98">
+        <v>148</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>150000</v>
+      </c>
+      <c r="I98">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99">
+        <v>202</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>10000</v>
+      </c>
+      <c r="I99">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100">
+        <v>7</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100">
+        <v>52</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>5000</v>
+      </c>
+      <c r="I100">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>10000</v>
+      </c>
+      <c r="I101">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>113</v>
+      </c>
+      <c r="C102">
+        <v>148</v>
+      </c>
+      <c r="E102">
         <v>1</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
+      <c r="G102">
+        <v>15000</v>
+      </c>
+      <c r="I102">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>114</v>
+      </c>
+      <c r="C103">
+        <v>18</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>15000</v>
+      </c>
+      <c r="I103">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104">
+        <v>26</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>15000</v>
+      </c>
+      <c r="I104">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>116</v>
+      </c>
+      <c r="C105">
+        <v>148</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>15000</v>
+      </c>
+      <c r="I105">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>117</v>
+      </c>
+      <c r="C106">
+        <v>25</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="G106">
+        <v>15000</v>
+      </c>
+      <c r="I106">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107">
+        <v>12</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>15000</v>
+      </c>
+      <c r="I107">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>15000</v>
+      </c>
+      <c r="I108">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109">
+        <v>14</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="G109">
+        <v>15000</v>
+      </c>
+      <c r="I109">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>15000</v>
+      </c>
+      <c r="I110">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111">
+        <v>22</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>15000</v>
+      </c>
+      <c r="I111">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112">
+        <v>9</v>
+      </c>
+      <c r="B112" t="s">
+        <v>123</v>
+      </c>
+      <c r="C112">
+        <v>263</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113">
+        <v>7</v>
+      </c>
+      <c r="B113" t="s">
+        <v>124</v>
+      </c>
+      <c r="C113">
+        <v>198</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>5000</v>
+      </c>
+      <c r="I113">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114">
+        <v>7</v>
+      </c>
+      <c r="B114" t="s">
+        <v>125</v>
+      </c>
+      <c r="C114">
+        <v>216</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>5000</v>
+      </c>
+      <c r="I114">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>126</v>
+      </c>
+      <c r="C115">
+        <v>79</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>5000</v>
+      </c>
+      <c r="I115">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>127</v>
+      </c>
+      <c r="C116">
+        <v>263</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>20000</v>
+      </c>
+      <c r="I116">
         <v>50000</v>
       </c>
-      <c r="K20" t="s">
-        <v>19</v>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117">
+        <v>4</v>
+      </c>
+      <c r="B117" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117">
+        <v>263</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>20000</v>
+      </c>
+      <c r="I117">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118">
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>129</v>
+      </c>
+      <c r="C118">
+        <v>263</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>15000</v>
+      </c>
+      <c r="I118">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>130</v>
+      </c>
+      <c r="C119">
+        <v>28</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>5000</v>
+      </c>
+      <c r="I119">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>5000</v>
+      </c>
+      <c r="I120">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121">
+        <v>7</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>5000</v>
+      </c>
+      <c r="I121">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122">
+        <v>7</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122">
+        <v>263</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>5000</v>
+      </c>
+      <c r="I122">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123">
+        <v>7</v>
+      </c>
+      <c r="B123" t="s">
+        <v>134</v>
+      </c>
+      <c r="C123">
+        <v>186</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>5000</v>
+      </c>
+      <c r="I123">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124">
+        <v>7</v>
+      </c>
+      <c r="B124" t="s">
+        <v>135</v>
+      </c>
+      <c r="C124">
+        <v>32</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>5000</v>
+      </c>
+      <c r="I124">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125">
+        <v>24</v>
+      </c>
+      <c r="B125" t="s">
+        <v>136</v>
+      </c>
+      <c r="C125">
+        <v>266</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126">
+        <v>24</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126">
+        <v>266</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>25000</v>
+      </c>
+      <c r="I126">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>138</v>
+      </c>
+      <c r="C127">
+        <v>188</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>25000</v>
+      </c>
+      <c r="I127">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128">
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>139</v>
+      </c>
+      <c r="C128">
+        <v>14</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>5000</v>
+      </c>
+      <c r="I128">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129">
+        <v>28</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>190000</v>
+      </c>
+      <c r="I129">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130">
+        <v>4</v>
+      </c>
+      <c r="B130" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130">
+        <v>27</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>15000</v>
+      </c>
+      <c r="I130">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131">
+        <v>255</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>5000</v>
+      </c>
+      <c r="I131">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132">
+        <v>4</v>
+      </c>
+      <c r="B132" t="s">
+        <v>143</v>
+      </c>
+      <c r="C132">
+        <v>32</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>15000</v>
+      </c>
+      <c r="I132">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133">
+        <v>7</v>
+      </c>
+      <c r="B133" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133">
+        <v>27</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>10000</v>
+      </c>
+      <c r="I133">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134">
+        <v>4</v>
+      </c>
+      <c r="B134" t="s">
+        <v>145</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>50000</v>
+      </c>
+      <c r="I134">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>146</v>
+      </c>
+      <c r="C135">
+        <v>20</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>10000</v>
+      </c>
+      <c r="I135">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>148</v>
+      </c>
+      <c r="C137">
+        <v>177</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>5000</v>
+      </c>
+      <c r="I137">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>149</v>
+      </c>
+      <c r="C138">
+        <v>97</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>5000</v>
+      </c>
+      <c r="I138">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>150</v>
+      </c>
+      <c r="C139">
+        <v>34</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>25000</v>
+      </c>
+      <c r="I139">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>151</v>
+      </c>
+      <c r="C140">
+        <v>277</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>5000</v>
+      </c>
+      <c r="I140">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>152</v>
+      </c>
+      <c r="C141">
+        <v>83</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>5000</v>
+      </c>
+      <c r="I141">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>153</v>
+      </c>
+      <c r="C142">
+        <v>278</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>5000</v>
+      </c>
+      <c r="I142">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>154</v>
+      </c>
+      <c r="C143">
+        <v>7</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>5000</v>
+      </c>
+      <c r="I143">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>155</v>
+      </c>
+      <c r="C144">
+        <v>73</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>5000</v>
+      </c>
+      <c r="I144">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>156</v>
+      </c>
+      <c r="C145">
+        <v>269</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>5000</v>
+      </c>
+      <c r="I145">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146">
+        <v>5</v>
+      </c>
+      <c r="B146" t="s">
+        <v>157</v>
+      </c>
+      <c r="C146">
+        <v>73</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147">
+        <v>7</v>
+      </c>
+      <c r="B147" t="s">
+        <v>158</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>5000</v>
+      </c>
+      <c r="I147">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>159</v>
+      </c>
+      <c r="C148">
+        <v>289</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>10000</v>
+      </c>
+      <c r="I148">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>160</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>3000</v>
+      </c>
+      <c r="I149">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>161</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>7000</v>
+      </c>
+      <c r="I150">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151">
+        <v>7</v>
+      </c>
+      <c r="B151" t="s">
+        <v>162</v>
+      </c>
+      <c r="C151">
+        <v>266</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>5000</v>
+      </c>
+      <c r="I151">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152">
+        <v>7</v>
+      </c>
+      <c r="B152" t="s">
+        <v>163</v>
+      </c>
+      <c r="C152">
+        <v>41</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>5000</v>
+      </c>
+      <c r="I152">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153">
+        <v>27</v>
+      </c>
+      <c r="B153" t="s">
+        <v>164</v>
+      </c>
+      <c r="C153">
+        <v>22</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>200000</v>
+      </c>
+      <c r="K153">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154">
+        <v>7</v>
+      </c>
+      <c r="B154" t="s">
+        <v>165</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>5000</v>
+      </c>
+      <c r="I154">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155">
+        <v>7</v>
+      </c>
+      <c r="B155" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155">
+        <v>12</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>5000</v>
+      </c>
+      <c r="I155">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156">
+        <v>73</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>20000</v>
+      </c>
+      <c r="I156">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>168</v>
+      </c>
+      <c r="C157">
+        <v>10</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>35000</v>
+      </c>
+      <c r="I157">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158">
+        <v>7</v>
+      </c>
+      <c r="B158" t="s">
+        <v>169</v>
+      </c>
+      <c r="C158">
+        <v>278</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>5000</v>
+      </c>
+      <c r="I158">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159">
+        <v>7</v>
+      </c>
+      <c r="B159" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159">
+        <v>299</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>10000</v>
+      </c>
+      <c r="I159">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160">
+        <v>7</v>
+      </c>
+      <c r="B160" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160">
+        <v>38</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>5000</v>
+      </c>
+      <c r="I160">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161">
+        <v>7</v>
+      </c>
+      <c r="B161" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161">
+        <v>260</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="G161">
+        <v>5000</v>
+      </c>
+      <c r="I161">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162">
+        <v>4</v>
+      </c>
+      <c r="B162" t="s">
+        <v>173</v>
+      </c>
+      <c r="C162">
+        <v>47</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>15000</v>
+      </c>
+      <c r="I162">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163">
+        <v>7</v>
+      </c>
+      <c r="B163" t="s">
+        <v>174</v>
+      </c>
+      <c r="C163">
+        <v>238</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>5000</v>
+      </c>
+      <c r="I163">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164">
+        <v>7</v>
+      </c>
+      <c r="B164" t="s">
+        <v>175</v>
+      </c>
+      <c r="C164">
+        <v>238</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>10000</v>
+      </c>
+      <c r="I164">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165">
+        <v>7</v>
+      </c>
+      <c r="B165" t="s">
+        <v>176</v>
+      </c>
+      <c r="C165">
+        <v>307</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>5000</v>
+      </c>
+      <c r="I165">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166">
+        <v>4</v>
+      </c>
+      <c r="B166" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166">
+        <v>37</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>20000</v>
+      </c>
+      <c r="I166">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167">
+        <v>7</v>
+      </c>
+      <c r="B167" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167">
+        <v>234</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>10000</v>
+      </c>
+      <c r="I167">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168">
+        <v>7</v>
+      </c>
+      <c r="B168" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168">
+        <v>208</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>5000</v>
+      </c>
+      <c r="I168">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169">
+        <v>7</v>
+      </c>
+      <c r="B169" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169">
+        <v>32</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>10000</v>
+      </c>
+      <c r="I169">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170">
+        <v>7</v>
+      </c>
+      <c r="B170" t="s">
+        <v>181</v>
+      </c>
+      <c r="C170">
+        <v>447</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>5000</v>
+      </c>
+      <c r="I170">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171">
+        <v>7</v>
+      </c>
+      <c r="B171" t="s">
+        <v>182</v>
+      </c>
+      <c r="C171">
+        <v>219</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>5000</v>
+      </c>
+      <c r="I171">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172">
+        <v>7</v>
+      </c>
+      <c r="B172" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172">
+        <v>2</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>10000</v>
+      </c>
+      <c r="I172">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173">
+        <v>7</v>
+      </c>
+      <c r="B173" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173">
+        <v>12</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>5000</v>
+      </c>
+      <c r="I173">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174">
+        <v>7</v>
+      </c>
+      <c r="B174" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174">
+        <v>20</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>15000</v>
+      </c>
+      <c r="I174">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175">
+        <v>5</v>
+      </c>
+      <c r="B175" t="s">
+        <v>186</v>
+      </c>
+      <c r="C175">
+        <v>20</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>20000</v>
+      </c>
+      <c r="I175">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176">
+        <v>4</v>
+      </c>
+      <c r="B176" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176">
+        <v>94</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>20000</v>
+      </c>
+      <c r="I176">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177">
+        <v>7</v>
+      </c>
+      <c r="B177" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177">
+        <v>317</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>5000</v>
+      </c>
+      <c r="I177">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178">
+        <v>7</v>
+      </c>
+      <c r="B178" t="s">
+        <v>189</v>
+      </c>
+      <c r="C178">
+        <v>40</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>5000</v>
+      </c>
+      <c r="I178">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179">
+        <v>7</v>
+      </c>
+      <c r="B179" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179">
+        <v>452</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="G179">
+        <v>5000</v>
+      </c>
+      <c r="I179">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180">
+        <v>5</v>
+      </c>
+      <c r="B180" t="s">
+        <v>191</v>
+      </c>
+      <c r="C180">
+        <v>147</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <v>20000</v>
+      </c>
+      <c r="I180">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181">
+        <v>5</v>
+      </c>
+      <c r="B181" t="s">
+        <v>192</v>
+      </c>
+      <c r="C181">
+        <v>9</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>10000</v>
+      </c>
+      <c r="I181">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182">
+        <v>7</v>
+      </c>
+      <c r="B182" t="s">
+        <v>193</v>
+      </c>
+      <c r="C182">
+        <v>55</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="G182">
+        <v>5000</v>
+      </c>
+      <c r="I182">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183">
+        <v>4</v>
+      </c>
+      <c r="B183" t="s">
+        <v>194</v>
+      </c>
+      <c r="C183">
+        <v>291</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>20000</v>
+      </c>
+      <c r="I183">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184">
+        <v>7</v>
+      </c>
+      <c r="B184" t="s">
+        <v>195</v>
+      </c>
+      <c r="C184">
+        <v>15</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>5000</v>
+      </c>
+      <c r="I184">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185">
+        <v>7</v>
+      </c>
+      <c r="B185" t="s">
+        <v>196</v>
+      </c>
+      <c r="C185">
+        <v>161</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>5000</v>
+      </c>
+      <c r="I185">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186">
+        <v>7</v>
+      </c>
+      <c r="B186" t="s">
+        <v>197</v>
+      </c>
+      <c r="C186">
+        <v>289</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>5000</v>
+      </c>
+      <c r="I186">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187">
+        <v>7</v>
+      </c>
+      <c r="B187" t="s">
+        <v>198</v>
+      </c>
+      <c r="C187">
+        <v>7</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="G187">
+        <v>5000</v>
+      </c>
+      <c r="I187">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188">
+        <v>7</v>
+      </c>
+      <c r="B188" t="s">
+        <v>199</v>
+      </c>
+      <c r="C188">
+        <v>2</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+      <c r="G188">
+        <v>10000</v>
+      </c>
+      <c r="I188">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189">
+        <v>7</v>
+      </c>
+      <c r="B189" t="s">
+        <v>200</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+      <c r="G189">
+        <v>10000</v>
+      </c>
+      <c r="I189">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190">
+        <v>7</v>
+      </c>
+      <c r="B190" t="s">
+        <v>201</v>
+      </c>
+      <c r="C190">
+        <v>12</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>5000</v>
+      </c>
+      <c r="I190">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191">
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>202</v>
+      </c>
+      <c r="C191">
+        <v>12</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <v>65000</v>
+      </c>
+      <c r="I191">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192">
+        <v>7</v>
+      </c>
+      <c r="B192" t="s">
+        <v>203</v>
+      </c>
+      <c r="C192">
+        <v>81</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <v>5000</v>
+      </c>
+      <c r="I192">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193">
+        <v>7</v>
+      </c>
+      <c r="B193" t="s">
+        <v>204</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="E193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>5000</v>
+      </c>
+      <c r="I193">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12">
+      <c r="A194">
+        <v>7</v>
+      </c>
+      <c r="B194" t="s">
+        <v>205</v>
+      </c>
+      <c r="C194">
+        <v>12</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>5000</v>
+      </c>
+      <c r="I194">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195">
+        <v>7</v>
+      </c>
+      <c r="B195" t="s">
+        <v>206</v>
+      </c>
+      <c r="C195">
+        <v>383</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="G195">
+        <v>5000</v>
+      </c>
+      <c r="I195">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196">
+        <v>7</v>
+      </c>
+      <c r="B196" t="s">
+        <v>207</v>
+      </c>
+      <c r="C196">
+        <v>53</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>10000</v>
+      </c>
+      <c r="I196">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197">
+        <v>5</v>
+      </c>
+      <c r="B197" t="s">
+        <v>208</v>
+      </c>
+      <c r="C197">
+        <v>69</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="G197">
+        <v>50000</v>
+      </c>
+      <c r="I197">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198">
+        <v>5</v>
+      </c>
+      <c r="B198" t="s">
+        <v>209</v>
+      </c>
+      <c r="C198">
+        <v>473</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="G198">
+        <v>25000</v>
+      </c>
+      <c r="I198">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199">
+        <v>7</v>
+      </c>
+      <c r="B199" t="s">
+        <v>210</v>
+      </c>
+      <c r="C199">
+        <v>37</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>5000</v>
+      </c>
+      <c r="I199">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200">
+        <v>7</v>
+      </c>
+      <c r="B200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C200">
+        <v>71</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>5000</v>
+      </c>
+      <c r="I200">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201">
+        <v>4</v>
+      </c>
+      <c r="B201" t="s">
+        <v>212</v>
+      </c>
+      <c r="C201">
+        <v>47</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>20000</v>
+      </c>
+      <c r="I201">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202">
+        <v>7</v>
+      </c>
+      <c r="B202" t="s">
+        <v>213</v>
+      </c>
+      <c r="C202">
+        <v>47</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>5000</v>
+      </c>
+      <c r="I202">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203">
+        <v>4</v>
+      </c>
+      <c r="B203" t="s">
+        <v>214</v>
+      </c>
+      <c r="C203">
+        <v>47</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>25000</v>
+      </c>
+      <c r="I203">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12">
+      <c r="A204">
+        <v>5</v>
+      </c>
+      <c r="B204" t="s">
+        <v>215</v>
+      </c>
+      <c r="C204">
+        <v>47</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>10000</v>
+      </c>
+      <c r="I204">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205">
+        <v>7</v>
+      </c>
+      <c r="B205" t="s">
+        <v>216</v>
+      </c>
+      <c r="C205">
+        <v>242</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>40000</v>
+      </c>
+      <c r="I205">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206">
+        <v>4</v>
+      </c>
+      <c r="B206" t="s">
+        <v>217</v>
+      </c>
+      <c r="C206">
+        <v>28</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>15000</v>
+      </c>
+      <c r="I206">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207">
+        <v>7</v>
+      </c>
+      <c r="B207" t="s">
+        <v>218</v>
+      </c>
+      <c r="C207">
+        <v>480</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>50000</v>
+      </c>
+      <c r="I207">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208">
+        <v>7</v>
+      </c>
+      <c r="B208" t="s">
+        <v>219</v>
+      </c>
+      <c r="C208">
+        <v>68</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>5000</v>
+      </c>
+      <c r="I208">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12">
+      <c r="A209">
+        <v>7</v>
+      </c>
+      <c r="B209" t="s">
+        <v>220</v>
+      </c>
+      <c r="C209">
+        <v>34</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>5000</v>
+      </c>
+      <c r="I209">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12">
+      <c r="A210">
+        <v>7</v>
+      </c>
+      <c r="B210" t="s">
+        <v>221</v>
+      </c>
+      <c r="C210">
+        <v>43</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>5000</v>
+      </c>
+      <c r="I210">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12">
+      <c r="A211">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>222</v>
+      </c>
+      <c r="C211">
+        <v>41</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12">
+      <c r="A212">
+        <v>4</v>
+      </c>
+      <c r="B212" t="s">
+        <v>223</v>
+      </c>
+      <c r="C212">
+        <v>41</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
+      <c r="A213">
+        <v>5</v>
+      </c>
+      <c r="B213" t="s">
+        <v>224</v>
+      </c>
+      <c r="C213">
+        <v>208</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12">
+      <c r="A214">
+        <v>7</v>
+      </c>
+      <c r="B214" t="s">
+        <v>225</v>
+      </c>
+      <c r="C214">
+        <v>12</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>5000</v>
+      </c>
+      <c r="I214">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12">
+      <c r="A215">
+        <v>7</v>
+      </c>
+      <c r="B215" t="s">
+        <v>226</v>
+      </c>
+      <c r="C215">
+        <v>292</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>5000</v>
+      </c>
+      <c r="I215">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12">
+      <c r="A216">
+        <v>7</v>
+      </c>
+      <c r="B216" t="s">
+        <v>227</v>
+      </c>
+      <c r="C216">
+        <v>12</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>5000</v>
+      </c>
+      <c r="I216">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
+      <c r="A217">
+        <v>4</v>
+      </c>
+      <c r="B217" t="s">
+        <v>228</v>
+      </c>
+      <c r="C217">
+        <v>275</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>15000</v>
+      </c>
+      <c r="I217">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12">
+      <c r="A218">
+        <v>4</v>
+      </c>
+      <c r="B218" t="s">
+        <v>229</v>
+      </c>
+      <c r="C218">
+        <v>275</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>20000</v>
+      </c>
+      <c r="I218">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12">
+      <c r="A219">
+        <v>5</v>
+      </c>
+      <c r="B219" t="s">
+        <v>230</v>
+      </c>
+      <c r="C219">
+        <v>88</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>10000</v>
+      </c>
+      <c r="I219">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12">
+      <c r="A220">
+        <v>4</v>
+      </c>
+      <c r="B220" t="s">
+        <v>231</v>
+      </c>
+      <c r="C220">
+        <v>20</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12">
+      <c r="A221">
+        <v>4</v>
+      </c>
+      <c r="B221" t="s">
+        <v>232</v>
+      </c>
+      <c r="C221">
+        <v>18</v>
+      </c>
+      <c r="D221">
+        <v>1234567</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="G221">
+        <v>340000</v>
+      </c>
+      <c r="I221">
+        <v>400000</v>
+      </c>
+      <c r="K221">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222">
+        <v>7</v>
+      </c>
+      <c r="B222" t="s">
+        <v>233</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="E222">
+        <v>2</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>5500</v>
+      </c>
+      <c r="H222">
+        <v>100000</v>
+      </c>
+      <c r="I222">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12">
+      <c r="A223">
+        <v>27</v>
+      </c>
+      <c r="B223" t="s">
+        <v>234</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223" t="s">
+        <v>235</v>
+      </c>
+      <c r="E223">
+        <v>9</v>
+      </c>
+      <c r="G223">
+        <v>50000</v>
+      </c>
+      <c r="H223">
+        <v>65000</v>
+      </c>
+      <c r="I223">
+        <v>95000</v>
+      </c>
+      <c r="K223">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
